--- a/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
+++ b/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T10:08:45+00:00</t>
+    <t>2026-04-21T12:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
+++ b/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T12:35:07+00:00</t>
+    <t>2026-04-21T14:23:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
+++ b/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:23:21+00:00</t>
+    <t>2026-04-21T15:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
+++ b/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T15:20:56+00:00</t>
+    <t>2026-04-21T17:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
+++ b/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:28:39+00:00</t>
+    <t>2026-04-21T21:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
+++ b/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T21:04:33+00:00</t>
+    <t>2026-04-23T08:11:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
+++ b/dataAbsentAndEmptyReason/ig/mappingEvenementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:11:47+00:00</t>
+    <t>2026-04-23T14:59:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
